--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ175"/>
+  <dimension ref="A1:AZ177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14774,57 +14774,60 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122384362</v>
+        <v>136921478</v>
       </c>
       <c r="B119" t="n">
-        <v>5199</v>
+        <v>58169</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>650453</v>
+        <v>650135</v>
       </c>
       <c r="R119" t="n">
-        <v>6674307</v>
+        <v>6674234</v>
       </c>
       <c r="S119" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14848,22 +14851,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14889,16 +14892,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384362</t>
+          <t>https://artportalen.se/Sighting/136921478</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122399627</v>
+        <v>136921477</v>
       </c>
       <c r="B120" t="n">
-        <v>5199</v>
+        <v>58164</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14906,16 +14909,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -14923,15 +14926,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -14939,13 +14941,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>650420</v>
+        <v>650023</v>
       </c>
       <c r="R120" t="n">
-        <v>6673617</v>
+        <v>6674170</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14969,22 +14971,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15010,13 +15012,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399627</t>
+          <t>https://artportalen.se/Sighting/136921477</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122399628</v>
+        <v>122384362</v>
       </c>
       <c r="B121" t="n">
         <v>5199</v>
@@ -15056,14 +15058,14 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>650379</v>
+        <v>650453</v>
       </c>
       <c r="R121" t="n">
-        <v>6673641</v>
+        <v>6674307</v>
       </c>
       <c r="S121" t="n">
         <v>4</v>
@@ -15090,22 +15092,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15131,13 +15133,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399628</t>
+          <t>https://artportalen.se/Sighting/122384362</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122399630</v>
+        <v>122399627</v>
       </c>
       <c r="B122" t="n">
         <v>5199</v>
@@ -15171,7 +15173,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -15181,10 +15183,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>650217</v>
+        <v>650420</v>
       </c>
       <c r="R122" t="n">
-        <v>6673709</v>
+        <v>6673617</v>
       </c>
       <c r="S122" t="n">
         <v>4</v>
@@ -15216,7 +15218,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15226,7 +15228,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15252,13 +15254,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399630</t>
+          <t>https://artportalen.se/Sighting/122399627</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123812917</v>
+        <v>122399628</v>
       </c>
       <c r="B123" t="n">
         <v>5199</v>
@@ -15302,10 +15304,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>650398</v>
+        <v>650379</v>
       </c>
       <c r="R123" t="n">
-        <v>6674100</v>
+        <v>6673641</v>
       </c>
       <c r="S123" t="n">
         <v>4</v>
@@ -15332,22 +15334,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15373,13 +15375,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123812917</t>
+          <t>https://artportalen.se/Sighting/122399628</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123812918</v>
+        <v>122399630</v>
       </c>
       <c r="B124" t="n">
         <v>5199</v>
@@ -15413,7 +15415,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -15423,10 +15425,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>649981</v>
+        <v>650217</v>
       </c>
       <c r="R124" t="n">
-        <v>6674147</v>
+        <v>6673709</v>
       </c>
       <c r="S124" t="n">
         <v>4</v>
@@ -15453,22 +15455,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15494,13 +15496,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123812918</t>
+          <t>https://artportalen.se/Sighting/122399630</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123812919</v>
+        <v>123812917</v>
       </c>
       <c r="B125" t="n">
         <v>5199</v>
@@ -15544,10 +15546,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>650544</v>
+        <v>650398</v>
       </c>
       <c r="R125" t="n">
-        <v>6674029</v>
+        <v>6674100</v>
       </c>
       <c r="S125" t="n">
         <v>4</v>
@@ -15579,7 +15581,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15589,7 +15591,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15615,13 +15617,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123812919</t>
+          <t>https://artportalen.se/Sighting/123812917</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>123812920</v>
+        <v>123812918</v>
       </c>
       <c r="B126" t="n">
         <v>5199</v>
@@ -15665,10 +15667,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>650569</v>
+        <v>649981</v>
       </c>
       <c r="R126" t="n">
-        <v>6674036</v>
+        <v>6674147</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -15700,7 +15702,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15710,7 +15712,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15736,13 +15738,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123812920</t>
+          <t>https://artportalen.se/Sighting/123812918</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>123812922</v>
+        <v>123812919</v>
       </c>
       <c r="B127" t="n">
         <v>5199</v>
@@ -15786,10 +15788,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>650359</v>
+        <v>650544</v>
       </c>
       <c r="R127" t="n">
-        <v>6673745</v>
+        <v>6674029</v>
       </c>
       <c r="S127" t="n">
         <v>4</v>
@@ -15821,7 +15823,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15831,7 +15833,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15857,13 +15859,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123812922</t>
+          <t>https://artportalen.se/Sighting/123812919</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>123812923</v>
+        <v>123812920</v>
       </c>
       <c r="B128" t="n">
         <v>5199</v>
@@ -15897,7 +15899,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -15907,10 +15909,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>650382</v>
+        <v>650569</v>
       </c>
       <c r="R128" t="n">
-        <v>6673978</v>
+        <v>6674036</v>
       </c>
       <c r="S128" t="n">
         <v>4</v>
@@ -15942,7 +15944,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15952,7 +15954,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15978,13 +15980,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123812923</t>
+          <t>https://artportalen.se/Sighting/123812920</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>123812924</v>
+        <v>123812922</v>
       </c>
       <c r="B129" t="n">
         <v>5199</v>
@@ -16018,20 +16020,20 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Ängen, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>650459</v>
+        <v>650359</v>
       </c>
       <c r="R129" t="n">
-        <v>6674278</v>
+        <v>6673745</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
@@ -16063,7 +16065,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16073,7 +16075,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16099,63 +16101,60 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123812924</t>
+          <t>https://artportalen.se/Sighting/123812922</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122384472</v>
+        <v>123812923</v>
       </c>
       <c r="B130" t="n">
-        <v>99118</v>
+        <v>5199</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>650415</v>
+        <v>650382</v>
       </c>
       <c r="R130" t="n">
-        <v>6674360</v>
+        <v>6673978</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
@@ -16182,22 +16181,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16223,63 +16222,60 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384472</t>
+          <t>https://artportalen.se/Sighting/123812923</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122384473</v>
+        <v>123812924</v>
       </c>
       <c r="B131" t="n">
-        <v>99118</v>
+        <v>5199</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Ängen, Upl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>650400</v>
+        <v>650459</v>
       </c>
       <c r="R131" t="n">
-        <v>6674415</v>
+        <v>6674278</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -16306,22 +16302,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16347,13 +16343,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384473</t>
+          <t>https://artportalen.se/Sighting/123812924</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122384476</v>
+        <v>122384472</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -16383,7 +16379,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -16396,14 +16392,14 @@
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>650396</v>
+        <v>650415</v>
       </c>
       <c r="R132" t="n">
-        <v>6674252</v>
+        <v>6674360</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
@@ -16435,7 +16431,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16445,7 +16441,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16471,13 +16467,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384476</t>
+          <t>https://artportalen.se/Sighting/122384472</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122384477</v>
+        <v>122384473</v>
       </c>
       <c r="B133" t="n">
         <v>99118</v>
@@ -16507,7 +16503,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16520,14 +16516,14 @@
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>650415</v>
+        <v>650400</v>
       </c>
       <c r="R133" t="n">
-        <v>6674216</v>
+        <v>6674415</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -16559,7 +16555,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16569,7 +16565,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16595,13 +16591,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384477</t>
+          <t>https://artportalen.se/Sighting/122384473</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122399666</v>
+        <v>122384476</v>
       </c>
       <c r="B134" t="n">
         <v>99118</v>
@@ -16631,10 +16627,14 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>650369</v>
+        <v>650396</v>
       </c>
       <c r="R134" t="n">
-        <v>6673665</v>
+        <v>6674252</v>
       </c>
       <c r="S134" t="n">
         <v>4</v>
@@ -16674,27 +16674,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16720,13 +16715,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399666</t>
+          <t>https://artportalen.se/Sighting/122384476</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122399667</v>
+        <v>122384477</v>
       </c>
       <c r="B135" t="n">
         <v>99118</v>
@@ -16756,7 +16751,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16773,10 +16768,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>650365</v>
+        <v>650415</v>
       </c>
       <c r="R135" t="n">
-        <v>6673701</v>
+        <v>6674216</v>
       </c>
       <c r="S135" t="n">
         <v>4</v>
@@ -16803,22 +16798,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16844,13 +16839,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399667</t>
+          <t>https://artportalen.se/Sighting/122384477</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122399668</v>
+        <v>122399666</v>
       </c>
       <c r="B136" t="n">
         <v>99118</v>
@@ -16880,14 +16875,10 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
@@ -16897,10 +16888,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>650331</v>
+        <v>650369</v>
       </c>
       <c r="R136" t="n">
-        <v>6673701</v>
+        <v>6673665</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -16932,7 +16923,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16942,12 +16933,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Minst! Orkar inte räkna mer här.</t>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16973,13 +16964,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399668</t>
+          <t>https://artportalen.se/Sighting/122399666</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122399670</v>
+        <v>122399667</v>
       </c>
       <c r="B137" t="n">
         <v>99118</v>
@@ -17009,7 +17000,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -17026,10 +17017,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>650313</v>
+        <v>650365</v>
       </c>
       <c r="R137" t="n">
-        <v>6673680</v>
+        <v>6673701</v>
       </c>
       <c r="S137" t="n">
         <v>4</v>
@@ -17061,7 +17052,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17071,7 +17062,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17097,13 +17088,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399670</t>
+          <t>https://artportalen.se/Sighting/122399667</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>123813009</v>
+        <v>122399668</v>
       </c>
       <c r="B138" t="n">
         <v>99118</v>
@@ -17133,7 +17124,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17150,10 +17141,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>650385</v>
+        <v>650331</v>
       </c>
       <c r="R138" t="n">
-        <v>6673957</v>
+        <v>6673701</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -17180,22 +17171,27 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Minst! Orkar inte räkna mer här.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17221,13 +17217,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813009</t>
+          <t>https://artportalen.se/Sighting/122399668</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>123813011</v>
+        <v>122399670</v>
       </c>
       <c r="B139" t="n">
         <v>99118</v>
@@ -17257,7 +17253,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17274,10 +17270,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>650499</v>
+        <v>650313</v>
       </c>
       <c r="R139" t="n">
-        <v>6673899</v>
+        <v>6673680</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -17304,22 +17300,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17345,13 +17341,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813011</t>
+          <t>https://artportalen.se/Sighting/122399670</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>123813014</v>
+        <v>123813009</v>
       </c>
       <c r="B140" t="n">
         <v>99118</v>
@@ -17381,7 +17377,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17398,10 +17394,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>650344</v>
+        <v>650385</v>
       </c>
       <c r="R140" t="n">
-        <v>6673730</v>
+        <v>6673957</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -17433,7 +17429,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17443,12 +17439,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17474,13 +17465,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813014</t>
+          <t>https://artportalen.se/Sighting/123813009</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129135118</v>
+        <v>123813011</v>
       </c>
       <c r="B141" t="n">
         <v>99118</v>
@@ -17510,7 +17501,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17527,10 +17518,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>650395</v>
+        <v>650499</v>
       </c>
       <c r="R141" t="n">
-        <v>6673800</v>
+        <v>6673899</v>
       </c>
       <c r="S141" t="n">
         <v>4</v>
@@ -17557,22 +17548,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17598,13 +17589,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135118</t>
+          <t>https://artportalen.se/Sighting/123813011</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129135122</v>
+        <v>123813014</v>
       </c>
       <c r="B142" t="n">
         <v>99118</v>
@@ -17634,7 +17625,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -17651,10 +17642,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>650361</v>
+        <v>650344</v>
       </c>
       <c r="R142" t="n">
-        <v>6673754</v>
+        <v>6673730</v>
       </c>
       <c r="S142" t="n">
         <v>4</v>
@@ -17681,22 +17672,27 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17722,55 +17718,63 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135122</t>
+          <t>https://artportalen.se/Sighting/123813014</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>122384487</v>
+        <v>129135118</v>
       </c>
       <c r="B143" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>650442</v>
+        <v>650395</v>
       </c>
       <c r="R143" t="n">
-        <v>6674345</v>
+        <v>6673800</v>
       </c>
       <c r="S143" t="n">
         <v>4</v>
@@ -17797,22 +17801,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17838,48 +17842,48 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384487</t>
+          <t>https://artportalen.se/Sighting/129135118</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122399676</v>
+        <v>129135122</v>
       </c>
       <c r="B144" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -17891,10 +17895,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>650299</v>
+        <v>650361</v>
       </c>
       <c r="R144" t="n">
-        <v>6673755</v>
+        <v>6673754</v>
       </c>
       <c r="S144" t="n">
         <v>4</v>
@@ -17921,22 +17925,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17962,63 +17966,55 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399676</t>
+          <t>https://artportalen.se/Sighting/129135122</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129135132</v>
+        <v>122384487</v>
       </c>
       <c r="B145" t="n">
-        <v>102240</v>
+        <v>106244</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>650406</v>
+        <v>650442</v>
       </c>
       <c r="R145" t="n">
-        <v>6674252</v>
+        <v>6674345</v>
       </c>
       <c r="S145" t="n">
         <v>4</v>
@@ -18045,22 +18041,22 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18086,16 +18082,16 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135132</t>
+          <t>https://artportalen.se/Sighting/122384487</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122384479</v>
+        <v>122399676</v>
       </c>
       <c r="B146" t="n">
-        <v>101326</v>
+        <v>106244</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18103,38 +18099,46 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>650415</v>
+        <v>650299</v>
       </c>
       <c r="R146" t="n">
-        <v>6674370</v>
+        <v>6673755</v>
       </c>
       <c r="S146" t="n">
         <v>4</v>
@@ -18161,22 +18165,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18202,42 +18206,50 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384479</t>
+          <t>https://artportalen.se/Sighting/122399676</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122384480</v>
+        <v>129135132</v>
       </c>
       <c r="B147" t="n">
-        <v>101326</v>
+        <v>102240</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -18247,10 +18259,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>650316</v>
+        <v>650406</v>
       </c>
       <c r="R147" t="n">
-        <v>6674034</v>
+        <v>6674252</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -18277,22 +18289,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18318,13 +18330,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384480</t>
+          <t>https://artportalen.se/Sighting/129135132</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122384481</v>
+        <v>122384479</v>
       </c>
       <c r="B148" t="n">
         <v>101326</v>
@@ -18359,14 +18371,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>650230</v>
+        <v>650415</v>
       </c>
       <c r="R148" t="n">
-        <v>6674064</v>
+        <v>6674370</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -18398,7 +18410,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18408,7 +18420,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18434,13 +18446,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384481</t>
+          <t>https://artportalen.se/Sighting/122384479</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122384483</v>
+        <v>122384480</v>
       </c>
       <c r="B149" t="n">
         <v>101326</v>
@@ -18479,10 +18491,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>650238</v>
+        <v>650316</v>
       </c>
       <c r="R149" t="n">
-        <v>6674076</v>
+        <v>6674034</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -18514,7 +18526,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18524,7 +18536,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18550,13 +18562,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384483</t>
+          <t>https://artportalen.se/Sighting/122384480</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122384484</v>
+        <v>122384481</v>
       </c>
       <c r="B150" t="n">
         <v>101326</v>
@@ -18595,10 +18607,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>650407</v>
+        <v>650230</v>
       </c>
       <c r="R150" t="n">
-        <v>6674068</v>
+        <v>6674064</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -18630,7 +18642,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18640,7 +18652,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18666,13 +18678,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384484</t>
+          <t>https://artportalen.se/Sighting/122384481</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122384485</v>
+        <v>122384483</v>
       </c>
       <c r="B151" t="n">
         <v>101326</v>
@@ -18711,10 +18723,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>650432</v>
+        <v>650238</v>
       </c>
       <c r="R151" t="n">
-        <v>6674247</v>
+        <v>6674076</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -18746,7 +18758,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18756,7 +18768,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18782,13 +18794,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122384485</t>
+          <t>https://artportalen.se/Sighting/122384483</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122399671</v>
+        <v>122384484</v>
       </c>
       <c r="B152" t="n">
         <v>101326</v>
@@ -18827,10 +18839,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>650309</v>
+        <v>650407</v>
       </c>
       <c r="R152" t="n">
-        <v>6673789</v>
+        <v>6674068</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -18857,22 +18869,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18898,13 +18910,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399671</t>
+          <t>https://artportalen.se/Sighting/122384484</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122399672</v>
+        <v>122384485</v>
       </c>
       <c r="B153" t="n">
         <v>101326</v>
@@ -18943,10 +18955,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>650329</v>
+        <v>650432</v>
       </c>
       <c r="R153" t="n">
-        <v>6673994</v>
+        <v>6674247</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -18973,22 +18985,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -19014,13 +19026,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399672</t>
+          <t>https://artportalen.se/Sighting/122384485</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122399673</v>
+        <v>122399671</v>
       </c>
       <c r="B154" t="n">
         <v>101326</v>
@@ -19059,10 +19071,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>650321</v>
+        <v>650309</v>
       </c>
       <c r="R154" t="n">
-        <v>6673981</v>
+        <v>6673789</v>
       </c>
       <c r="S154" t="n">
         <v>4</v>
@@ -19094,7 +19106,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -19104,7 +19116,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19130,13 +19142,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399673</t>
+          <t>https://artportalen.se/Sighting/122399671</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122399674</v>
+        <v>122399672</v>
       </c>
       <c r="B155" t="n">
         <v>101326</v>
@@ -19175,10 +19187,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>650187</v>
+        <v>650329</v>
       </c>
       <c r="R155" t="n">
-        <v>6674052</v>
+        <v>6673994</v>
       </c>
       <c r="S155" t="n">
         <v>4</v>
@@ -19210,7 +19222,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -19220,7 +19232,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19246,13 +19258,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399674</t>
+          <t>https://artportalen.se/Sighting/122399672</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122399675</v>
+        <v>122399673</v>
       </c>
       <c r="B156" t="n">
         <v>101326</v>
@@ -19291,10 +19303,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>650473</v>
+        <v>650321</v>
       </c>
       <c r="R156" t="n">
-        <v>6673911</v>
+        <v>6673981</v>
       </c>
       <c r="S156" t="n">
         <v>4</v>
@@ -19326,7 +19338,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -19336,7 +19348,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19362,13 +19374,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122399675</t>
+          <t>https://artportalen.se/Sighting/122399673</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>123813016</v>
+        <v>122399674</v>
       </c>
       <c r="B157" t="n">
         <v>101326</v>
@@ -19398,11 +19410,7 @@
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -19411,10 +19419,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>650418</v>
+        <v>650187</v>
       </c>
       <c r="R157" t="n">
-        <v>6674028</v>
+        <v>6674052</v>
       </c>
       <c r="S157" t="n">
         <v>4</v>
@@ -19441,22 +19449,22 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19482,13 +19490,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813016</t>
+          <t>https://artportalen.se/Sighting/122399674</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>123813019</v>
+        <v>122399675</v>
       </c>
       <c r="B158" t="n">
         <v>101326</v>
@@ -19527,10 +19535,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>649964</v>
+        <v>650473</v>
       </c>
       <c r="R158" t="n">
-        <v>6674228</v>
+        <v>6673911</v>
       </c>
       <c r="S158" t="n">
         <v>4</v>
@@ -19557,22 +19565,22 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19598,13 +19606,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813019</t>
+          <t>https://artportalen.se/Sighting/122399675</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>123813054</v>
+        <v>123813016</v>
       </c>
       <c r="B159" t="n">
         <v>101326</v>
@@ -19634,7 +19642,11 @@
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
@@ -19643,10 +19655,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>649938</v>
+        <v>650418</v>
       </c>
       <c r="R159" t="n">
-        <v>6674212</v>
+        <v>6674028</v>
       </c>
       <c r="S159" t="n">
         <v>4</v>
@@ -19678,7 +19690,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19688,7 +19700,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19714,13 +19726,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813054</t>
+          <t>https://artportalen.se/Sighting/123813016</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>123813056</v>
+        <v>123813019</v>
       </c>
       <c r="B160" t="n">
         <v>101326</v>
@@ -19759,10 +19771,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>649986</v>
+        <v>649964</v>
       </c>
       <c r="R160" t="n">
-        <v>6674182</v>
+        <v>6674228</v>
       </c>
       <c r="S160" t="n">
         <v>4</v>
@@ -19794,7 +19806,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19804,7 +19816,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19830,13 +19842,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813056</t>
+          <t>https://artportalen.se/Sighting/123813019</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>123813058</v>
+        <v>123813054</v>
       </c>
       <c r="B161" t="n">
         <v>101326</v>
@@ -19875,10 +19887,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>649973</v>
+        <v>649938</v>
       </c>
       <c r="R161" t="n">
-        <v>6674181</v>
+        <v>6674212</v>
       </c>
       <c r="S161" t="n">
         <v>4</v>
@@ -19910,7 +19922,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19920,7 +19932,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19946,13 +19958,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813058</t>
+          <t>https://artportalen.se/Sighting/123813054</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>123813061</v>
+        <v>123813056</v>
       </c>
       <c r="B162" t="n">
         <v>101326</v>
@@ -19991,10 +20003,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>650032</v>
+        <v>649986</v>
       </c>
       <c r="R162" t="n">
-        <v>6674145</v>
+        <v>6674182</v>
       </c>
       <c r="S162" t="n">
         <v>4</v>
@@ -20026,7 +20038,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -20036,7 +20048,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -20062,13 +20074,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813061</t>
+          <t>https://artportalen.se/Sighting/123813056</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>123813062</v>
+        <v>123813058</v>
       </c>
       <c r="B163" t="n">
         <v>101326</v>
@@ -20107,10 +20119,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>650089</v>
+        <v>649973</v>
       </c>
       <c r="R163" t="n">
-        <v>6674165</v>
+        <v>6674181</v>
       </c>
       <c r="S163" t="n">
         <v>4</v>
@@ -20142,7 +20154,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20152,7 +20164,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20178,13 +20190,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813062</t>
+          <t>https://artportalen.se/Sighting/123813058</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>123813064</v>
+        <v>123813061</v>
       </c>
       <c r="B164" t="n">
         <v>101326</v>
@@ -20223,10 +20235,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>650552</v>
+        <v>650032</v>
       </c>
       <c r="R164" t="n">
-        <v>6674009</v>
+        <v>6674145</v>
       </c>
       <c r="S164" t="n">
         <v>4</v>
@@ -20258,7 +20270,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20268,7 +20280,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20294,13 +20306,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813064</t>
+          <t>https://artportalen.se/Sighting/123813061</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>123813065</v>
+        <v>123813062</v>
       </c>
       <c r="B165" t="n">
         <v>101326</v>
@@ -20339,10 +20351,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>650528</v>
+        <v>650089</v>
       </c>
       <c r="R165" t="n">
-        <v>6674007</v>
+        <v>6674165</v>
       </c>
       <c r="S165" t="n">
         <v>4</v>
@@ -20374,7 +20386,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20384,7 +20396,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20410,13 +20422,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813065</t>
+          <t>https://artportalen.se/Sighting/123813062</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>123813066</v>
+        <v>123813064</v>
       </c>
       <c r="B166" t="n">
         <v>101326</v>
@@ -20455,10 +20467,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>650396</v>
+        <v>650552</v>
       </c>
       <c r="R166" t="n">
-        <v>6673744</v>
+        <v>6674009</v>
       </c>
       <c r="S166" t="n">
         <v>4</v>
@@ -20490,7 +20502,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20500,7 +20512,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20526,13 +20538,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813066</t>
+          <t>https://artportalen.se/Sighting/123813064</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>123813068</v>
+        <v>123813065</v>
       </c>
       <c r="B167" t="n">
         <v>101326</v>
@@ -20571,10 +20583,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>650397</v>
+        <v>650528</v>
       </c>
       <c r="R167" t="n">
-        <v>6674135</v>
+        <v>6674007</v>
       </c>
       <c r="S167" t="n">
         <v>4</v>
@@ -20606,7 +20618,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20616,7 +20628,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20642,13 +20654,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813068</t>
+          <t>https://artportalen.se/Sighting/123813065</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>123813069</v>
+        <v>123813066</v>
       </c>
       <c r="B168" t="n">
         <v>101326</v>
@@ -20687,10 +20699,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>649962</v>
+        <v>650396</v>
       </c>
       <c r="R168" t="n">
-        <v>6674252</v>
+        <v>6673744</v>
       </c>
       <c r="S168" t="n">
         <v>4</v>
@@ -20722,7 +20734,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20732,7 +20744,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20758,16 +20770,16 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123813069</t>
+          <t>https://artportalen.se/Sighting/123813066</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129135124</v>
+        <v>123813068</v>
       </c>
       <c r="B169" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20799,14 +20811,14 @@
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Skarbo, Upl</t>
+          <t>Slåttsved, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>650418</v>
+        <v>650397</v>
       </c>
       <c r="R169" t="n">
-        <v>6674276</v>
+        <v>6674135</v>
       </c>
       <c r="S169" t="n">
         <v>4</v>
@@ -20833,22 +20845,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20874,16 +20886,16 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135124</t>
+          <t>https://artportalen.se/Sighting/123813068</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129135125</v>
+        <v>123813069</v>
       </c>
       <c r="B170" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20919,10 +20931,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>650422</v>
+        <v>649962</v>
       </c>
       <c r="R170" t="n">
-        <v>6674261</v>
+        <v>6674252</v>
       </c>
       <c r="S170" t="n">
         <v>4</v>
@@ -20949,22 +20961,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20990,13 +21002,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135125</t>
+          <t>https://artportalen.se/Sighting/123813069</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129135126</v>
+        <v>129135124</v>
       </c>
       <c r="B171" t="n">
         <v>101325</v>
@@ -21031,14 +21043,14 @@
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Slåttsved, Upl</t>
+          <t>Skarbo, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>650374</v>
+        <v>650418</v>
       </c>
       <c r="R171" t="n">
-        <v>6673996</v>
+        <v>6674276</v>
       </c>
       <c r="S171" t="n">
         <v>4</v>
@@ -21070,7 +21082,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21080,7 +21092,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21106,13 +21118,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135126</t>
+          <t>https://artportalen.se/Sighting/129135124</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129135128</v>
+        <v>129135125</v>
       </c>
       <c r="B172" t="n">
         <v>101325</v>
@@ -21151,10 +21163,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>650424</v>
+        <v>650422</v>
       </c>
       <c r="R172" t="n">
-        <v>6673873</v>
+        <v>6674261</v>
       </c>
       <c r="S172" t="n">
         <v>4</v>
@@ -21186,7 +21198,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -21196,7 +21208,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21222,13 +21234,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135128</t>
+          <t>https://artportalen.se/Sighting/129135125</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129135129</v>
+        <v>129135126</v>
       </c>
       <c r="B173" t="n">
         <v>101325</v>
@@ -21267,10 +21279,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>650431</v>
+        <v>650374</v>
       </c>
       <c r="R173" t="n">
-        <v>6673874</v>
+        <v>6673996</v>
       </c>
       <c r="S173" t="n">
         <v>4</v>
@@ -21302,7 +21314,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -21312,7 +21324,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21338,13 +21350,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135129</t>
+          <t>https://artportalen.se/Sighting/129135126</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129135130</v>
+        <v>129135128</v>
       </c>
       <c r="B174" t="n">
         <v>101325</v>
@@ -21383,10 +21395,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>650409</v>
+        <v>650424</v>
       </c>
       <c r="R174" t="n">
-        <v>6673720</v>
+        <v>6673873</v>
       </c>
       <c r="S174" t="n">
         <v>4</v>
@@ -21418,7 +21430,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -21428,7 +21440,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21454,13 +21466,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135130</t>
+          <t>https://artportalen.se/Sighting/129135128</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129135131</v>
+        <v>129135129</v>
       </c>
       <c r="B175" t="n">
         <v>101325</v>
@@ -21499,10 +21511,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>650359</v>
+        <v>650431</v>
       </c>
       <c r="R175" t="n">
-        <v>6673996</v>
+        <v>6673874</v>
       </c>
       <c r="S175" t="n">
         <v>4</v>
@@ -21534,7 +21546,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21544,7 +21556,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21569,6 +21581,238 @@
       </c>
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135129</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>129135130</v>
+      </c>
+      <c r="B176" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>650409</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6673720</v>
+      </c>
+      <c r="S176" t="n">
+        <v>4</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135130</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>129135131</v>
+      </c>
+      <c r="B177" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Slåttsved, Upl</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>650359</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6673996</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129135131</t>
         </is>
@@ -21750,6 +21994,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -14777,7 +14777,7 @@
         <v>136921478</v>
       </c>
       <c r="B119" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>136921477</v>
       </c>
       <c r="B120" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -14777,7 +14777,7 @@
         <v>136921478</v>
       </c>
       <c r="B119" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>136921477</v>
       </c>
       <c r="B120" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -14809,11 +14809,7 @@
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -14777,7 +14777,7 @@
         <v>136921478</v>
       </c>
       <c r="B119" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>136921477</v>
       </c>
       <c r="B120" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -14777,7 +14777,7 @@
         <v>136921478</v>
       </c>
       <c r="B119" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>136921477</v>
       </c>
       <c r="B120" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 162-2025 artfynd.xlsx
+++ b/artfynd/A 162-2025 artfynd.xlsx
@@ -14777,7 +14777,7 @@
         <v>136921478</v>
       </c>
       <c r="B119" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>136921477</v>
       </c>
       <c r="B120" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
